--- a/processed_ruby_restored_xlsx/sc222_瑠璃４：花火.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc222_瑠璃４：花火.ss.xlsx
@@ -710,8 +710,8 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan let out a tiny laugh only I could hear,
-and twined her pinky with mine...</t>
+          <t>Rurichiyo-chan let out a tiny laugh only I could
+hear, and twined her pinky with mine...</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -742,8 +742,8 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>Taking that as our cue, we linked hands like lovers so
-no one else would notice.</t>
+          <t>Taking that as our cue, we linked hands like lovers
+so no one else would notice.</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -909,8 +909,8 @@
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>...Everyone, totally hyped up, called out and tried to
-outdo one another.</t>
+          <t>...Everyone, totally hyped up, called out and tried
+to outdo one another.</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1033,7 +1033,8 @@
       <c r="B38" s="1" t="inlineStr">
         <is>
           <t>While I was smiling at everyone more than the
-fireworks, Rurichiyo-chan gave me a scolding — "Hey！".</t>
+fireworks, Rurichiyo-chan gave me a scolding —
+"Hey！".</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1384,8 +1385,8 @@
       <c r="B61" s="1" t="inlineStr">
         <is>
           <t>No, no — the wallet I had tucked in my sash had
-shifted in a weird way and was just pushing up against
-that area.</t>
+shifted in a weird way and was just pushing up
+against that area.</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1508,7 +1509,8 @@
       <c r="B69" s="1" t="inlineStr">
         <is>
           <t>I tried to laugh it off, but before I could,
-Rurichiyo-chan said it sadly and I hurriedly retorted.</t>
+Rurichiyo-chan said it sadly and I hurriedly
+retorted.</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -2401,8 +2403,8 @@
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>Thinking that, my penis starts trembling... there's no
-way I'm going to clear this up now！</t>
+          <t>Thinking that, my penis starts trembling... there's
+no way I'm going to clear this up now！</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -2815,8 +2817,8 @@
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>...The hair tie that had been holding Rurichiyo-chan's
-beautiful hair was on my penis...！</t>
+          <t>...The hair tie that had been holding
+Rurichiyo-chan's beautiful hair was on my penis...！</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -2861,8 +2863,8 @@
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>In no time my penis was rock hard, veins even standing
-out.</t>
+          <t>In no time my penis was rock hard, veins even
+standing out.</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -2984,8 +2986,8 @@
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>「No, um... well, you see？ I thought if you squeezed it
-like 'gyuu~' it would go limp...」</t>
+          <t>「No, um... well, you see？ I thought if you squeezed
+it like 'gyuu~' it would go limp...」</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -3248,8 +3250,8 @@
       </c>
       <c r="B182" s="1" t="inlineStr">
         <is>
-          <t>Just as expected, but mixed with the loud booms of the
-fireworks, I could hear everyone else's excited
+          <t>Just as expected, but mixed with the loud booms of
+the fireworks, I could hear everyone else's excited
 shouts.</t>
         </is>
       </c>
@@ -4108,8 +4110,8 @@
       </c>
       <c r="B238" s="1" t="inlineStr">
         <is>
-          <t>It’s probably Rurichiyo-chan’s own kind of punishment,
-but my pleasure just keeps building.</t>
+          <t>It’s probably Rurichiyo-chan’s own kind of
+punishment, but my pleasure just keeps building.</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -4491,8 +4493,8 @@
       </c>
       <c r="B263" s="1" t="inlineStr">
         <is>
-          <t>The stimulation, far stronger than I'd expected, makes
-me involuntarily cry out loudly.</t>
+          <t>The stimulation, far stronger than I'd expected,
+makes me involuntarily cry out loudly.</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -4783,8 +4785,8 @@
       </c>
       <c r="B282" s="1" t="inlineStr">
         <is>
-          <t>Having the head, already sensitized by so many kisses,
-tormented even more is unbearable.</t>
+          <t>Having the head, already sensitized by so many
+kisses, tormented even more is unbearable.</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -4875,7 +4877,8 @@
       </c>
       <c r="B288" s="1" t="inlineStr">
         <is>
-          <t>As for me, there's nothing I can do about it anymore….</t>
+          <t>As for me, there's nothing I can do about it
+anymore….</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -5102,7 +5105,8 @@
       </c>
       <c r="B303" s="1" t="inlineStr">
         <is>
-          <t>「Nnff, I must…hold back… chu, chup！ Chub, chuu… chum！」</t>
+          <t>「Nnff, I must…hold back… chu, chup！ Chub, chuu…
+chum！」</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -5286,7 +5290,8 @@
       </c>
       <c r="B315" s="1" t="inlineStr">
         <is>
-          <t>「Hmm！ What MiruMiru's holding is hard to pass up too…」</t>
+          <t>「Hmm！ What MiruMiru's holding is hard to pass up
+too…」</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -5316,7 +5321,8 @@
       </c>
       <c r="B317" s="1" t="inlineStr">
         <is>
-          <t>「Let's each buy different ones… and split them later.」</t>
+          <t>「Let's each buy different ones… and split them
+later.」</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -5376,8 +5382,9 @@
       </c>
       <c r="B321" s="1" t="inlineStr">
         <is>
-          <t>It seems they're so caught up in the fireworks and the
-dagashi that they haven't noticed us slipping away.</t>
+          <t>It seems they're so caught up in the fireworks and
+the dagashi that they haven't noticed us slipping
+away.</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -5590,8 +5597,8 @@
       </c>
       <c r="B335" s="1" t="inlineStr">
         <is>
-          <t>「Ru, Rurichiyo-chan... I don't think I can hold on...！
-Maybe I can't...」</t>
+          <t>「Ru, Rurichiyo-chan... I don't think I can hold
+on...！ Maybe I can't...」</t>
         </is>
       </c>
       <c r="C335" t="n">
@@ -5667,8 +5674,8 @@
       </c>
       <c r="B340" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan's tongue work is noticeably more heated
-than before.</t>
+          <t>Rurichiyo-chan's tongue work is noticeably more
+heated than before.</t>
         </is>
       </c>
       <c r="C340" t="n">
@@ -5744,7 +5751,8 @@
       </c>
       <c r="B345" s="1" t="inlineStr">
         <is>
-          <t>「Chupuu... chuppaa, n'fu！ Chu chuuu... chu, chu！ Chu！」</t>
+          <t>「Chupuu... chuppaa, n'fu！ Chu chuuu... chu, chu！
+Chu！」</t>
         </is>
       </c>
       <c r="C345" t="n">
@@ -6038,8 +6046,8 @@
       </c>
       <c r="B364" s="1" t="inlineStr">
         <is>
-          <t>「Chu... nnn！ It's twitching... I'm coming, wa, amu！ N~
-chuchu！」</t>
+          <t>「Chu... nnn！ It's twitching... I'm coming, wa, amu！
+N~ chuchu！」</t>
         </is>
       </c>
       <c r="C364" t="n">
@@ -6408,8 +6416,8 @@
       </c>
       <c r="B388" s="1" t="inlineStr">
         <is>
-          <t>「Fufu… fuh！ chu-pah！ chuuu… chu！ gucchuu, guchu！ chuu…
-chupa, chu！」</t>
+          <t>「Fufu… fuh！ chu-pah！ chuuu… chu！ gucchuu, guchu！
+chuu… chupa, chu！」</t>
         </is>
       </c>
       <c r="C388" t="n">
@@ -6454,8 +6462,8 @@
       </c>
       <c r="B391" s="1" t="inlineStr">
         <is>
-          <t>Only pleasure keeps accelerating and there's nothing I
-can do about it…！</t>
+          <t>Only pleasure keeps accelerating and there's nothing
+I can do about it…！</t>
         </is>
       </c>
       <c r="C391" t="n">
@@ -6485,7 +6493,8 @@
       </c>
       <c r="B393" s="1" t="inlineStr">
         <is>
-          <t>As if she can tell I'm at my limit and can't hold on…！</t>
+          <t>As if she can tell I'm at my limit and can't hold
+on…！</t>
         </is>
       </c>
       <c r="C393" t="n">
@@ -6637,8 +6646,8 @@
       <c r="B403" s="1" t="inlineStr">
         <is>
           <t>The penis, having gone past its limit, overcame the
-hair tie’s tightness and expelled a lump of semen from
-deep inside…！</t>
+hair tie’s tightness and expelled a lump of semen
+from deep inside…！</t>
         </is>
       </c>
       <c r="C403" t="n">
@@ -6822,7 +6831,8 @@
       </c>
       <c r="B415" s="1" t="inlineStr">
         <is>
-          <t>But the penis keeps ejaculating without any restraint.</t>
+          <t>But the penis keeps ejaculating without any
+restraint.</t>
         </is>
       </c>
       <c r="C415" t="n">
@@ -6867,8 +6877,8 @@
       </c>
       <c r="B418" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan's cheek puffs out, and semen drips from
-the corner of her mouth.</t>
+          <t>Rurichiyo-chan's cheek puffs out, and semen drips
+from the corner of her mouth.</t>
         </is>
       </c>
       <c r="C418" t="n">
@@ -7187,8 +7197,8 @@
       </c>
       <c r="B439" s="1" t="inlineStr">
         <is>
-          <t>I could tell that from Rurichiyo-chan’s gesture, and I
-also noticed the change in her expression.</t>
+          <t>I could tell that from Rurichiyo-chan’s gesture, and
+I also noticed the change in her expression.</t>
         </is>
       </c>
       <c r="C439" t="n">
@@ -7480,7 +7490,8 @@
       <c r="B458" s="1" t="inlineStr">
         <is>
           <t>When the hair tie that had been squeezing my penis
-slipped off, the smoldering pleasure exploded outward.</t>
+slipped off, the smoldering pleasure exploded
+outward.</t>
         </is>
       </c>
       <c r="C458" t="n">
@@ -7800,8 +7811,8 @@
       </c>
       <c r="B479" s="1" t="inlineStr">
         <is>
-          <t>「Well then... right, yeah. Put your hands there... and
-face your butt that way, okay？」</t>
+          <t>「Well then... right, yeah. Put your hands there...
+and face your butt that way, okay？」</t>
         </is>
       </c>
       <c r="C479" t="n">
@@ -8350,8 +8361,8 @@
       </c>
       <c r="B515" s="1" t="inlineStr">
         <is>
-          <t>Either way, for now I can't help but say "good job" to
-Kikuchiyo-baa-chan.</t>
+          <t>Either way, for now I can't help but say "good job"
+to Kikuchiyo-baa-chan.</t>
         </is>
       </c>
       <c r="C515" t="n">
@@ -8472,8 +8483,8 @@
       </c>
       <c r="B523" s="1" t="inlineStr">
         <is>
-          <t>And her butt, trembling with shame, somehow looks like
-it's inviting me.</t>
+          <t>And her butt, trembling with shame, somehow looks
+like it's inviting me.</t>
         </is>
       </c>
       <c r="C523" t="n">
@@ -8729,8 +8740,8 @@
       </c>
       <c r="B540" s="1" t="inlineStr">
         <is>
-          <t>When I drag my finger along the seam, Rurichiyo-chan's
-momentum visibly drops.</t>
+          <t>When I drag my finger along the seam,
+Rurichiyo-chan's momentum visibly drops.</t>
         </is>
       </c>
       <c r="C540" t="n">
@@ -9052,8 +9063,8 @@
       </c>
       <c r="B561" s="1" t="inlineStr">
         <is>
-          <t>Meanwhile, my finger is feeling the heat of the thick,
-runny juice.</t>
+          <t>Meanwhile, my finger is feeling the heat of the
+thick, runny juice.</t>
         </is>
       </c>
       <c r="C561" t="n">
@@ -9115,8 +9126,8 @@
       </c>
       <c r="B565" s="1" t="inlineStr">
         <is>
-          <t>As if on cue, Rurichiyo-chan voiced what I was feeling
-for me.</t>
+          <t>As if on cue, Rurichiyo-chan voiced what I was
+feeling for me.</t>
         </is>
       </c>
       <c r="C565" t="n">
@@ -9360,7 +9371,8 @@
       </c>
       <c r="B581" s="1" t="inlineStr">
         <is>
-          <t>「Uauu...！ Ha, ha, ha... ha！ Emba...rrassed... desu...」</t>
+          <t>「Uauu...！ Ha, ha, ha... ha！ Emba...rrassed...
+desu...」</t>
         </is>
       </c>
       <c r="C581" t="n">
@@ -9376,7 +9388,8 @@
       <c r="B582" s="1" t="inlineStr">
         <is>
           <t>I suppress my excitement to set the mood, but
-Rurichiyo-chan already looks like she can’t hold back.</t>
+Rurichiyo-chan already looks like she can’t hold
+back.</t>
         </is>
       </c>
       <c r="C582" t="n">
@@ -9512,7 +9525,8 @@
       </c>
       <c r="B591" s="1" t="inlineStr">
         <is>
-          <t>「Ugh... nn！ Rurichiyo-chan, your voice... your voice！」</t>
+          <t>「Ugh... nn！ Rurichiyo-chan, your voice... your
+voice！」</t>
         </is>
       </c>
       <c r="C591" t="n">
@@ -9558,7 +9572,8 @@
       <c r="B594" s="1" t="inlineStr">
         <is>
           <t>I tried to subtly prompt her to be careful, but
-Rurichiyo-chan didn't seem to have any composure left.</t>
+Rurichiyo-chan didn't seem to have any composure
+left.</t>
         </is>
       </c>
       <c r="C594" t="n">
@@ -9633,8 +9648,8 @@
       </c>
       <c r="B599" s="1" t="inlineStr">
         <is>
-          <t>...Even though she was already wet, it wasn't loosened
-and the inside was painfully tight.</t>
+          <t>...Even though she was already wet, it wasn't
+loosened and the inside was painfully tight.</t>
         </is>
       </c>
       <c r="C599" t="n">
@@ -10156,8 +10171,8 @@
       </c>
       <c r="B633" s="1" t="inlineStr">
         <is>
-          <t>The thick part of my penis is being rubbed against the
-tight part of her pussy.</t>
+          <t>The thick part of my penis is being rubbed against
+the tight part of her pussy.</t>
         </is>
       </c>
       <c r="C633" t="n">
@@ -10738,8 +10753,8 @@
       </c>
       <c r="B671" s="1" t="inlineStr">
         <is>
-          <t>Trying to feel good together, the way we move our hips
-syncs more and more.</t>
+          <t>Trying to feel good together, the way we move our
+hips syncs more and more.</t>
         </is>
       </c>
       <c r="C671" t="n">
@@ -11249,8 +11264,8 @@
       </c>
       <c r="B704" s="1" t="inlineStr">
         <is>
-          <t>I could clearly see Rurichiyo-chan's face flush bright
-red, all the way to her ears.</t>
+          <t>I could clearly see Rurichiyo-chan's face flush
+bright red, all the way to her ears.</t>
         </is>
       </c>
       <c r="C704" t="n">
@@ -11265,8 +11280,8 @@
       </c>
       <c r="B705" s="1" t="inlineStr">
         <is>
-          <t>Her pussy was getting all wet and limp as she writhed,
-like she was drooling.</t>
+          <t>Her pussy was getting all wet and limp as she
+writhed, like she was drooling.</t>
         </is>
       </c>
       <c r="C705" t="n">
@@ -11420,8 +11435,8 @@
       </c>
       <c r="B715" s="1" t="inlineStr">
         <is>
-          <t>That penis had no self-control, twitching and bouncing
-up inside her pussy.</t>
+          <t>That penis had no self-control, twitching and
+bouncing up inside her pussy.</t>
         </is>
       </c>
       <c r="C715" t="n">
@@ -11451,7 +11466,8 @@
       </c>
       <c r="B717" s="1" t="inlineStr">
         <is>
-          <t>「Rurichiyo-chan... it's about time you got serious...」</t>
+          <t>「Rurichiyo-chan... it's about time you got
+serious...」</t>
         </is>
       </c>
       <c r="C717" t="n">
@@ -11787,8 +11803,8 @@
       </c>
       <c r="B739" s="1" t="inlineStr">
         <is>
-          <t>「Say things like that... Rurichiyo-chan... your butt's
-twitching too, isn't it...」</t>
+          <t>「Say things like that... Rurichiyo-chan... your
+butt's twitching too, isn't it...」</t>
         </is>
       </c>
       <c r="C739" t="n">
@@ -11911,7 +11927,8 @@
       </c>
       <c r="B747" s="1" t="inlineStr">
         <is>
-          <t>「I-I'm... me too... ah, un, nn！ Rurichi, yoo... chan！」</t>
+          <t>「I-I'm... me too... ah, un, nn！ Rurichi, yoo...
+chan！」</t>
         </is>
       </c>
       <c r="C747" t="n">
@@ -12017,7 +12034,8 @@
       </c>
       <c r="B754" s="1" t="inlineStr">
         <is>
-          <t>「I-I know... ah, nnhuuh！ It's no, it's no good... nn！」</t>
+          <t>「I-I know... ah, nnhuuh！ It's no, it's no good...
+nn！」</t>
         </is>
       </c>
       <c r="C754" t="n">
@@ -12064,8 +12082,8 @@
       </c>
       <c r="B757" s="1" t="inlineStr">
         <is>
-          <t>That very act sharpened their senses and only sped the
-pleasure...</t>
+          <t>That very act sharpened their senses and only sped
+the pleasure...</t>
         </is>
       </c>
       <c r="C757" t="n">
@@ -12110,9 +12128,9 @@
       </c>
       <c r="B760" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan’s expression, like she can’t hold it in
-anymore, is incredibly arousing and only makes me even
-more turned on.</t>
+          <t>Rurichiyo-chan’s expression, like she can’t hold it
+in anymore, is incredibly arousing and only makes me
+even more turned on.</t>
         </is>
       </c>
       <c r="C760" t="n">
@@ -12293,8 +12311,8 @@
       </c>
       <c r="B772" s="1" t="inlineStr">
         <is>
-          <t>...Every time I hear that voice, my body reacts on its
-own.</t>
+          <t>...Every time I hear that voice, my body reacts on
+its own.</t>
         </is>
       </c>
       <c r="C772" t="n">
@@ -12893,8 +12911,8 @@
       </c>
       <c r="B811" s="1" t="inlineStr">
         <is>
-          <t>「Y-you did really well holding it... right？ Good girl,
-good girl...」</t>
+          <t>「Y-you did really well holding it... right？ Good
+girl, good girl...」</t>
         </is>
       </c>
       <c r="C811" t="n">
@@ -13242,8 +13260,8 @@
       </c>
       <c r="B834" s="1" t="inlineStr">
         <is>
-          <t>But from the way everyone's talking, the fireworks are
-over too….</t>
+          <t>But from the way everyone's talking, the fireworks
+are over too….</t>
         </is>
       </c>
       <c r="C834" t="n">
@@ -13258,8 +13276,8 @@
       </c>
       <c r="B835" s="1" t="inlineStr">
         <is>
-          <t>After the fireworks are over, everyone will definitely
-be looking for us.</t>
+          <t>After the fireworks are over, everyone will
+definitely be looking for us.</t>
         </is>
       </c>
       <c r="C835" t="n">
@@ -13517,8 +13535,8 @@
       </c>
       <c r="B852" s="1" t="inlineStr">
         <is>
-          <t>A particularly big firework goes up at the end, and in
-that light Rurichiyo-chan's face becomes clear.</t>
+          <t>A particularly big firework goes up at the end, and
+in that light Rurichiyo-chan's face becomes clear.</t>
         </is>
       </c>
       <c r="C852" t="n">

--- a/processed_ruby_restored_xlsx/sc222_瑠璃４：花火.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc222_瑠璃４：花火.ss.xlsx
@@ -957,7 +957,7 @@
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>Hehe... she's so cute...！</t>
+          <t>Hehe... they're so cute...！</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>「Did I... do something？」</t>
+          <t>Did I... do something？</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>Maybe she was actually jealous...？</t>
+          <t>Maybe she was actually jealous...？"</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>She surprisingly has a strong possessiveness...？</t>
+          <t>She surprisingly has a strong possessiveness...？"</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -2019,7 +2019,7 @@
       <c r="B102" s="1" t="inlineStr">
         <is>
           <t>In that moment, the hem of my yukata was quickly
-brushed aside...！</t>
+brushed aside...！"</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -4002,8 +4002,8 @@
       </c>
       <c r="B231" s="1" t="inlineStr">
         <is>
-          <t>Because I tried to hold back, the tip actually became
-even more sensitive.</t>
+          <t>Because he tried to hold back, the tip actually
+became even more sensitive.</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="B234" s="1" t="inlineStr">
         <is>
-          <t>「Chuu... nn！ Chu！ Chu, dyuu...！ Dyu, dyudyu~...！」</t>
+          <t>Chuu... nn！ Chu！ Chu, dyuu...！ Dyu, dyudyu~...！</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="B240" s="1" t="inlineStr">
         <is>
-          <t>「Nn...hah！ Phew... um, Oji-sama？」</t>
+          <t>Nn...hah！ Phew... um, Oji-sama？</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="B336" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C336" t="n">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="B381" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C381" t="n">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="B387" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C387" t="n">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="B394" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C394" t="n">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B410" s="1" t="inlineStr">
         <is>
-          <t>「Haa, aaahhh... nngh, nnh！ Nnhah！」</t>
+          <t>Haa, aaahhh... nngh, nnh！ Nnhah！</t>
         </is>
       </c>
       <c r="C410" t="n">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="B417" s="1" t="inlineStr">
         <is>
-          <t>「Nngu…… k！ Goku…… gok！ Kuun……」</t>
+          <t>Nngu…… k！ Goku…… gok！ Kuun……</t>
         </is>
       </c>
       <c r="C417" t="n">
@@ -7338,7 +7338,7 @@
       <c r="B448" s="1" t="inlineStr">
         <is>
           <t>When Rurichiyo said that and she looked down at her
-own crotch, to her dismay my penis was still erect.</t>
+own crotch, to her dismay his penis was still erect.</t>
         </is>
       </c>
       <c r="C448" t="n">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="B453" s="1" t="inlineStr">
         <is>
-          <t>Perhaps satisfied after bringing me to orgasm once,
+          <t>Perhaps satisfied after bringing him to orgasm once,
 this time she nodded.</t>
         </is>
       </c>
@@ -7489,7 +7489,7 @@
       </c>
       <c r="B458" s="1" t="inlineStr">
         <is>
-          <t>When the hair tie that had been squeezing my penis
+          <t>When the hair tie that had been squeezing his penis
 slipped off, the smoldering pleasure exploded
 outward.</t>
         </is>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="B468" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C468" t="n">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="B474" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C474" t="n">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="B480" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C480" t="n">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="B488" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C488" t="n">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="B492" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C492" t="n">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="B497" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C497" t="n">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="B501" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C501" t="n">
@@ -8665,7 +8665,7 @@
       </c>
       <c r="B535" s="1" t="inlineStr">
         <is>
-          <t>「Fwah！」</t>
+          <t>Fwah！</t>
         </is>
       </c>
       <c r="C535" t="n">
@@ -9204,7 +9204,7 @@
       </c>
       <c r="B570" s="1" t="inlineStr">
         <is>
-          <t>But... should I give her one more push...？</t>
+          <t>But... should I give her one more push...？"</t>
         </is>
       </c>
       <c r="C570" t="n">
@@ -9908,8 +9908,8 @@
       </c>
       <c r="B616" s="1" t="inlineStr">
         <is>
-          <t>Trying to show my affection with my penis, I let
-momentum take over and then pulled my hips back...</t>
+          <t>Trying to show his affection with his penis, he let
+momentum take over and then pulled his hips back...</t>
         </is>
       </c>
       <c r="C616" t="n">
@@ -10034,7 +10034,7 @@
         <is>
           <t>My hips try to stop moving, but my penis’s excitement
 can’t be suppressed and it ends up trembling inside
-her vagina.</t>
+my vagina.</t>
         </is>
       </c>
       <c r="C624" t="n">
@@ -10094,8 +10094,8 @@
       </c>
       <c r="B628" s="1" t="inlineStr">
         <is>
-          <t>「Haa, nfuuh...！ For now... you have to hold back,
-okay？」</t>
+          <t>Haa, nfuuh...！ For now... you have to hold back,
+okay？</t>
         </is>
       </c>
       <c r="C628" t="n">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="B633" s="1" t="inlineStr">
         <is>
-          <t>The thick part of my penis is being rubbed against
+          <t>The thick part of his penis is being rubbed against
 the tight part of her pussy.</t>
         </is>
       </c>
@@ -10599,8 +10599,8 @@
       </c>
       <c r="B661" s="1" t="inlineStr">
         <is>
-          <t>Once I start moving, her pussy immediately begins to
-throb.</t>
+          <t>Once he starts moving, her pussy immediately begins
+to throb.</t>
         </is>
       </c>
       <c r="C661" t="n">
@@ -10924,8 +10924,8 @@
       </c>
       <c r="B682" s="1" t="inlineStr">
         <is>
-          <t>「Hah... hah... ugh！ My... my body is... moving on its
-own...」</t>
+          <t>Hah... hah... ugh！ My... my body is... moving on its
+own...</t>
         </is>
       </c>
       <c r="C682" t="n">
@@ -10986,7 +10986,7 @@
       </c>
       <c r="B686" s="1" t="inlineStr">
         <is>
-          <t>「Y-You...！　U-uhh...！」</t>
+          <t>Y-You...！　U-uhh...！</t>
         </is>
       </c>
       <c r="C686" t="n">
@@ -11186,9 +11186,9 @@
       </c>
       <c r="B699" s="1" t="inlineStr">
         <is>
-          <t>Her vaginal folds wrapped tightly around me, and from
-the gap where they were joined love juices leaked out
-like she’d wet herself.</t>
+          <t>Her vaginal folds wrapped tightly around him, and
+from the gap where they were joined love juices
+leaked out like she’d wet herself.</t>
         </is>
       </c>
       <c r="C699" t="n">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="B707" s="1" t="inlineStr">
         <is>
-          <t>「Nnnh！ Hah... Ochi, o—！ Penis...」</t>
+          <t>Nnnh！ Hah... Ochi, o—！ Penis...</t>
         </is>
       </c>
       <c r="C707" t="n">
@@ -11387,8 +11387,8 @@
       </c>
       <c r="B712" s="1" t="inlineStr">
         <is>
-          <t>「Hiu, n'aaah！ Inside, it twitched... ah, haaah！ The
-penis is twitching and twitching！ Ah, uun！」</t>
+          <t>Hiu, n'aaah！ Inside, it twitched... ah, haaah！ The
+penis is twitching and twitching！ Ah, uun！</t>
         </is>
       </c>
       <c r="C712" t="n">
@@ -11419,8 +11419,8 @@
       </c>
       <c r="B714" s="1" t="inlineStr">
         <is>
-          <t>Because she kept repeating “penis” over and over, it
-seems her resistance to the word started to loosen.</t>
+          <t>Because they kept repeating “penis” over and over, it
+seems their resistance to the word started to loosen.</t>
         </is>
       </c>
       <c r="C714" t="n">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="B730" s="1" t="inlineStr">
         <is>
-          <t>「Nn！ Nn-ha, mu！ Nn~fu, nnn~~ah！」</t>
+          <t>Nn！ Nn-ha, mu！ Nn~fu, nnn~~ah！</t>
         </is>
       </c>
       <c r="C730" t="n">
@@ -12235,8 +12235,7 @@
       </c>
       <c r="B767" s="1" t="inlineStr">
         <is>
-          <t>「Mmm... why don't we try waiting just a little
-longer？」</t>
+          <t>Mmm... why don't we try waiting just a little longer？</t>
         </is>
       </c>
       <c r="C767" t="n">
@@ -12512,8 +12511,8 @@
       </c>
       <c r="B785" s="1" t="inlineStr">
         <is>
-          <t>「Nmm, nnh！ This feels... so strange... it's, it's
-happening, shh！ Maa！ Hiu, hic...！」</t>
+          <t>Nmm, nnh！ This feels... so strange... it's, it's
+happening, shh！ Maa！ Hiu, hic...！</t>
         </is>
       </c>
       <c r="C785" t="n">
@@ -12591,7 +12590,7 @@
       </c>
       <c r="B790" s="1" t="inlineStr">
         <is>
-          <t>「Huh！ Huuu... c'mon, genka...！」</t>
+          <t>Huh！ Huuu... c'mon, genka...！</t>
         </is>
       </c>
       <c r="C790" t="n">
@@ -12606,7 +12605,7 @@
       </c>
       <c r="B791" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C791" t="n">
@@ -13229,7 +13228,7 @@
       </c>
       <c r="B832" s="1" t="inlineStr">
         <is>
-          <t>「I want to keep watching like this forever…」</t>
+          <t>I want to keep watching like this forever…</t>
         </is>
       </c>
       <c r="C832" t="n">
@@ -13337,7 +13336,7 @@
       </c>
       <c r="B839" s="1" t="inlineStr">
         <is>
-          <t>「Just a little longer, like this... okay？」</t>
+          <t>Just a little longer, like this... okay？</t>
         </is>
       </c>
       <c r="C839" t="n">
@@ -13367,7 +13366,7 @@
       </c>
       <c r="B841" s="1" t="inlineStr">
         <is>
-          <t>「Hah, f-fine...」</t>
+          <t>Hah, f-fine...</t>
         </is>
       </c>
       <c r="C841" t="n">
@@ -13414,8 +13413,8 @@
       </c>
       <c r="B844" s="1" t="inlineStr">
         <is>
-          <t>「Hehe, I want us to stay like this... together
-forever.」</t>
+          <t>Hehe, I want us to stay like this... together
+forever.</t>
         </is>
       </c>
       <c r="C844" t="n">
@@ -13475,7 +13474,7 @@
       </c>
       <c r="B848" s="1" t="inlineStr">
         <is>
-          <t>「Ah... my heart's still racing, huh」</t>
+          <t>Ah... my heart's still racing, huh</t>
         </is>
       </c>
       <c r="C848" t="n">
@@ -13505,7 +13504,7 @@
       </c>
       <c r="B850" s="1" t="inlineStr">
         <is>
-          <t>「Ufufu！ I... am too, you know~」</t>
+          <t>Ufufu！ I... am too, you know~</t>
         </is>
       </c>
       <c r="C850" t="n">
